--- a/scripts/test-data/test-data-005-mockpass-import-demo.xlsx
+++ b/scripts/test-data/test-data-005-mockpass-import-demo.xlsx
@@ -460,12 +460,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11.996339" customWidth="1" style="4" min="1" max="1"/>
     <col width="14.282054" customWidth="1" style="4" min="2" max="2"/>
-    <col width="15.282054" customWidth="1" style="4" min="3" max="3"/>
+    <col width="42" customWidth="1" style="4" min="3" max="3"/>
     <col width="28.139196" customWidth="1" style="4" min="4" max="4"/>
     <col width="11.424911" customWidth="1" style="5" min="5" max="5"/>
     <col width="15.282054" customWidth="1" style="4" min="6" max="6"/>
@@ -494,70 +494,75 @@
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
+          <t>MockPassPersonId</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
           <t>IdentityNumber</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>FullName</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>DateOfBirth</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>NationalityCode</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>CitizenshipStatusCode</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>StudentNumber</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>AcademicYear</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>LevelCode</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>ClassCode</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>StartDate</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="O1" s="6" t="inlineStr">
         <is>
           <t>Mobile</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="P1" s="6" t="inlineStr">
         <is>
           <t>Address</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="Q1" s="6" t="inlineStr">
         <is>
           <t>TemplateRow</t>
         </is>
@@ -570,61 +575,66 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
+          <t>78486d6b-3055-512e-8134-b9637f4b64f7</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
           <t>S7000101J</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Farah Rahman NUS</t>
         </is>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="F2" s="5" t="n">
         <v>37287</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-101</t>
         </is>
       </c>
-      <c r="I2" s="4" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J2" s="4" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>NUS-P6-21</t>
         </is>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="M2" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.farah.rahman.nus.101@student.example.test</t>
         </is>
       </c>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>+6591000101</t>
         </is>
       </c>
-      <c r="O2" s="4" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>101 Education Avenue, Singapore 100101</t>
         </is>
@@ -637,61 +647,66 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
+          <t>9419648b-5d20-5012-985e-b88cd419080d</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
           <t>S7000102K</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Gideon Koh NTU</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="F3" s="5" t="n">
         <v>40152</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-102</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>NTU-S2-21</t>
         </is>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="M3" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.gideon.koh.ntu.102@student.example.test</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>+6591000102</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>102 Education Avenue, Singapore 100102</t>
         </is>
@@ -704,61 +719,66 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
+          <t>db674358-e0d8-59f9-ae83-20b949239ab7</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
           <t>S7000103L</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Hazel Ng SMU</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>37094</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-103</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>SMU-UG-21</t>
         </is>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="M4" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.hazel.ng.smu.103@student.example.test</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>+6591000103</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>103 Education Avenue, Singapore 100103</t>
         </is>
@@ -771,61 +791,66 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
+          <t>7efc5640-5116-5d13-9b0d-bc119af7856c</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
           <t>S7000104M</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Isaac Chua SUTD</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="F5" s="5" t="n">
         <v>35506</v>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-104</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>SUTD-PG-21</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="M5" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.isaac.chua.sutd.104@student.example.test</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>+6591000104</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>104 Education Avenue, Singapore 100104</t>
         </is>
@@ -838,61 +863,66 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>82514335-2e1f-5a25-b9d4-e0b8d7fcdc00</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
           <t>S7000105N</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Jia Min Seah SIT</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="F6" s="5" t="n">
         <v>39730</v>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-105</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>SIT-DR-21</t>
         </is>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="M6" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.jia.min.seah.sit.105@student.example.test</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>+6591000105</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>105 Education Avenue, Singapore 100105</t>
         </is>
@@ -905,61 +935,66 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
+          <t>9f1a3858-7341-572d-8ba4-d28058c89780</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
           <t>S7000106P</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Keira Low NUS</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="F7" s="5" t="n">
         <v>37729</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-106</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>NUS-UG-22</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="M7" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.keira.low.nus.106@student.example.test</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>+6591000106</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>106 Education Avenue, Singapore 100106</t>
         </is>
@@ -972,61 +1007,66 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
+          <t>acc9166b-fae9-5697-8535-4235d61dbb0a</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
           <t>S7000107Q</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Leon Ho NTU</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="F8" s="5" t="n">
         <v>36336</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-107</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>NTU-PG-22</t>
         </is>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="M8" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.leon.ho.ntu.107@student.example.test</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>+6591000107</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>107 Education Avenue, Singapore 100107</t>
         </is>
@@ -1039,61 +1079,66 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>3c7f6b0b-2515-53c2-9038-10c21b07bc74</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
           <t>S7000108R</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Mira Das SMU</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="F9" s="5" t="n">
         <v>34676</v>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-108</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>SMU-DR-22</t>
         </is>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="M9" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.mira.das.smu.108@student.example.test</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>+6591000108</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>108 Education Avenue, Singapore 100108</t>
         </is>
@@ -1106,61 +1151,66 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
+          <t>58c10d9c-4daf-5538-b97c-0d6669ce2b1c</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
           <t>S7000109T</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Nolan Teo SUTD</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>38797</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-109</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>SUTD-S4-22</t>
         </is>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="M10" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.nolan.teo.sutd.109@student.example.test</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>+6591000109</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>109 Education Avenue, Singapore 100109</t>
         </is>
@@ -1173,61 +1223,66 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
+          <t>d52d8260-ed21-5cd3-b0a4-aed9563db9bd</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
           <t>S7000110U</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Olivia Chan SIT</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>40309</v>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-110</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>SIT-S3-22</t>
         </is>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="M11" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.olivia.chan.sit.110@student.example.test</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>+6591000110</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>110 Education Avenue, Singapore 100110</t>
         </is>
@@ -1240,61 +1295,66 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>d3e72b18-4441-5975-9f15-1a1d7f9b0d4b</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
           <t>S7000111V</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Pranav Menon NUS</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="F12" s="5" t="n">
         <v>36799</v>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-111</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>NUS-P6-23</t>
         </is>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="M12" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.pranav.menon.nus.111@student.example.test</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>+6591000111</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>111 Education Avenue, Singapore 100111</t>
         </is>
@@ -1307,61 +1367,66 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
+          <t>790f4ede-1561-59be-a542-e81004a61815</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
           <t>S7000112W</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Renee Yap NTU</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>35080</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-112</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>NTU-S2-23</t>
         </is>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="M13" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.renee.yap.ntu.112@student.example.test</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>+6591000112</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>112 Education Avenue, Singapore 100112</t>
         </is>
@@ -1374,61 +1439,66 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
+          <t>ff68d656-a21d-5110-b35f-eee03f87eb88</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
           <t>S7000113X</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Samuel Tay SMU</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="F14" s="5" t="n">
         <v>38175</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-113</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>SMU-UG-23</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="M14" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.samuel.tay.smu.113@student.example.test</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>+6591000113</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>113 Education Avenue, Singapore 100113</t>
         </is>
@@ -1441,61 +1511,66 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
+          <t>f6a3c2ee-b9d0-52aa-9166-506ab01992d5</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
           <t>S7000114Y</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Tara Nair SUTD</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="F15" s="5" t="n">
         <v>39775</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-114</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>SUTD-PG-23</t>
         </is>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="M15" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.tara.nair.sutd.114@student.example.test</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>+6591000114</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>114 Education Avenue, Singapore 100114</t>
         </is>
@@ -1508,61 +1583,66 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
+          <t>24426f58-35da-599e-8715-b0971abc4e0b</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
           <t>S7000115Z</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Vikram Singh SIT</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>37531</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-115</t>
         </is>
       </c>
-      <c r="I16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="K16" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>SIT-DR-23</t>
         </is>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="M16" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.vikram.singh.sit.115@student.example.test</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>+6591000115</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>115 Education Avenue, Singapore 100115</t>
         </is>
@@ -1575,61 +1655,66 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
+          <t>53fb5a5b-7f1b-5a53-9200-e4829677140d</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
           <t>S7000116A</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Avery Tan NUS</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="F17" s="5" t="n">
         <v>38029</v>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>NUS-2026-116</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>BACHELOR</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>NUS-UG-24</t>
         </is>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="M17" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.avery.tan.nus.116@student.example.test</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>+6591000116</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>116 Education Avenue, Singapore 100116</t>
         </is>
@@ -1642,61 +1727,66 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
+          <t>818808ca-3ac8-5160-8ce7-9425c895b3f9</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>S7000117B</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Bianca Lim NTU</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>36010</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>NTU-2026-117</t>
         </is>
       </c>
-      <c r="I18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="K18" s="4" t="inlineStr">
         <is>
           <t>MASTER</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>NTU-PG-24</t>
         </is>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="M18" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.bianca.lim.ntu.117@student.example.test</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>+6591000117</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
+      <c r="P18" s="4" t="inlineStr">
         <is>
           <t>117 Education Avenue, Singapore 100117</t>
         </is>
@@ -1707,63 +1797,64 @@
       <c r="B19" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>A7000118C</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Caleb Wong SMU</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="F19" s="5" t="n">
         <v>34292</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>SMU-2026-118</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>PHD</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>SMU-DR-24</t>
         </is>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="M19" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.caleb.wong.smu.118@student.example.test</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>+6591000118</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>118 Education Avenue, Singapore 100118</t>
         </is>
@@ -1776,57 +1867,62 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
+          <t>b7b60204-ce1a-52d7-83a2-521694f3def5</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
           <t>S7000119D</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="5" t="n">
         <v>38500</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>SUTD-2026-119</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>SUTD-S4-24</t>
         </is>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="M20" s="5" t="n">
         <v>46024</v>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.daphne.lee.sutd.119@student.example.test</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>+6591000119</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>119 Education Avenue, Singapore 100119</t>
         </is>
@@ -1839,61 +1935,66 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
+          <t>04ecd561-6681-5ed1-a803-c6a52963dd9f</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
           <t>S7000120E</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>QA TEST DEMO005 Elias Goh SIT</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="F21" s="5" t="n">
         <v>39339</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>CITIZEN</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>SIT-2026-120</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>POST_SEC</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>SIT-S3-24</t>
         </is>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="M21" s="5" t="n">
         <v>38974</v>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>qa.test.demo005.elias.goh.sit.120@student.example.test</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>+6591000120</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>120 Education Avenue, Singapore 100120</t>
         </is>
